--- a/poc/output/비교_As-Is_vs_K-Tieout.xlsx
+++ b/poc/output/비교_As-Is_vs_K-Tieout.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>11,135,814,030원 (100%) 중 3방향 일치 89.1%</t>
+          <t>11,135,814,030원 (100%) 중 3방향 일치 89.9%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1468,11 +1468,11 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>검토 필요 항목 확인 (건별 판단·회사 확인)</t>
+          <t>조회서 발송·회신 관리 (외부조회는 그대로 필요)</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>추정 배분·미배정 입금 확인</t>
+          <t>검토 필요 항목 확인 (건별 판단·회사 확인)</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1498,15 +1498,30 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>자동 생성 조서 검토·서명</t>
+          <t>추정 배분·미배정 입금 확인</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>K-Tieout</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>자동 생성 조서 검토·서명</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>건당 소요시간은 파일럿에서 실측해야 합니다. 데모 페이지에서 가정치를 바꿔 볼 수 있습니다.</t>
         </is>
